--- a/MEC/ADHERENT_Mechanical_BOM.xlsx
+++ b/MEC/ADHERENT_Mechanical_BOM.xlsx
@@ -1203,7 +1203,7 @@
         <x:v>LANE ROWS</x:v>
       </x:c>
       <x:c r="I24" s="26" t="str">
-        <x:v>Loaded/stall current, signal reference and reversal compatibility remain open.</x:v>
+        <x:v>Bench test at 24 V: 190 mA running, 280–310 mA braked, about 0.5 A stalled. Driven on/off by LANECTRL R1 high-side switches (no reversal). SIGNAL = 24 V dry contact; confirm pin reference on a real harness.</x:v>
       </x:c>
       <x:c r="J24" s="26" t="str">
         <x:v>Conveyor belt(CB002-24V-573mm).pdf</x:v>
